--- a/artfynd/A 60036-2022 artfynd.xlsx
+++ b/artfynd/A 60036-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60036-2022 artfynd.xlsx
+++ b/artfynd/A 60036-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98284275</v>
+        <v>98284053</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554332.8321520495</v>
+        <v>554349</v>
       </c>
       <c r="R2" t="n">
-        <v>6299679.697603135</v>
+        <v>6299667</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,19 +755,9 @@
           <t>2022-01-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98284259</v>
+        <v>98284072</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,7 +815,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554314.6254380113</v>
+        <v>554344</v>
       </c>
       <c r="R3" t="n">
-        <v>6299688.760450825</v>
+        <v>6299669</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,19 +865,9 @@
           <t>2022-01-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98284216</v>
+        <v>98284158</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +925,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554317.5651080053</v>
+        <v>554354</v>
       </c>
       <c r="R4" t="n">
-        <v>6299715.603653773</v>
+        <v>6299687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,19 +975,9 @@
           <t>2022-01-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,12 +1008,7 @@
         <v>98284173</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554354.7400484559</v>
+        <v>554355</v>
       </c>
       <c r="R5" t="n">
-        <v>6299681.076820677</v>
+        <v>6299681</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,19 +1085,9 @@
           <t>2022-01-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,15 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98284158</v>
+        <v>98284193</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1145,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1227,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554353.5656235458</v>
+        <v>554348</v>
       </c>
       <c r="R6" t="n">
-        <v>6299687.079000812</v>
+        <v>6299725</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,19 +1195,9 @@
           <t>2022-01-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98284239</v>
+        <v>98284216</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1255,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1352,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554306.9384794135</v>
+        <v>554317</v>
       </c>
       <c r="R7" t="n">
-        <v>6299689.754548844</v>
+        <v>6299716</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1385,19 +1305,9 @@
           <t>2022-01-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,15 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98284193</v>
+        <v>98284228</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1365,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1477,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554348.1348082523</v>
+        <v>554319</v>
       </c>
       <c r="R8" t="n">
-        <v>6299725.301085645</v>
+        <v>6299714</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1510,19 +1415,9 @@
           <t>2022-01-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,15 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98284228</v>
+        <v>98284239</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1475,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1602,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554319.2306002113</v>
+        <v>554307</v>
       </c>
       <c r="R9" t="n">
-        <v>6299713.984205066</v>
+        <v>6299689</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1635,19 +1525,9 @@
           <t>2022-01-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,15 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98284072</v>
+        <v>98284247</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1585,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1727,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554343.9355917858</v>
+        <v>554312</v>
       </c>
       <c r="R10" t="n">
-        <v>6299668.901224354</v>
+        <v>6299691</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,19 +1635,9 @@
           <t>2022-01-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,15 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98284265</v>
+        <v>98284259</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,7 +1695,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1852,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554321.750116801</v>
+        <v>554315</v>
       </c>
       <c r="R11" t="n">
-        <v>6299688.853135196</v>
+        <v>6299689</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1885,19 +1745,9 @@
           <t>2022-01-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,15 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98284270</v>
+        <v>98284265</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1805,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1977,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554325.6647603612</v>
+        <v>554322</v>
       </c>
       <c r="R12" t="n">
-        <v>6299682.886601333</v>
+        <v>6299689</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2010,19 +1855,9 @@
           <t>2022-01-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,15 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>98284247</v>
+        <v>98284270</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +1915,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2102,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554311.8567193474</v>
+        <v>554326</v>
       </c>
       <c r="R13" t="n">
-        <v>6299690.912602639</v>
+        <v>6299683</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2135,19 +1965,9 @@
           <t>2022-01-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2172,6 +1992,116 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>98284275</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Råddemåla 1:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>554333</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6299680</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-01-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-01-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60036-2022 artfynd.xlsx
+++ b/artfynd/A 60036-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284053</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284072</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284158</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284173</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284193</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284216</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284228</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284239</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284247</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284259</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1882,6 +1937,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284265</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284270</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2102,8 +2167,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98284275</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>